--- a/TestData/LV_T2327_TMTC0002473_VerifyTheRolesAvailableToRegistered.xlsx
+++ b/TestData/LV_T2327_TMTC0002473_VerifyTheRolesAvailableToRegistered.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vijay.kumar\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC7493A-00F3-46B0-84E3-098D6FA9FC72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B12140E-FCFB-4393-BF62-0468E4769237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -41,9 +41,6 @@
     <t>Opportunity</t>
   </si>
   <si>
-    <t>Project Tenex III</t>
-  </si>
-  <si>
     <t>Project Kelso XI</t>
   </si>
   <si>
@@ -60,6 +57,9 @@
   </si>
   <si>
     <t>James Craven</t>
+  </si>
+  <si>
+    <t>Project Peloton</t>
   </si>
 </sst>
 </file>
@@ -103,9 +103,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -387,14 +388,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -405,20 +406,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C3" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -430,19 +431,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0331C7F-1076-4045-A12F-645F65C1D829}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -453,19 +454,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EB80ABF-3E2D-4CF4-8352-E1A55C64BEA2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T2327_TMTC0002473_VerifyTheRolesAvailableToRegistered.xlsx
+++ b/TestData/LV_T2327_TMTC0002473_VerifyTheRolesAvailableToRegistered.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B12140E-FCFB-4393-BF62-0468E4769237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC4D0CC-EFF2-4363-9F4B-05C40ACC9AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>StdUser</t>
   </si>
@@ -60,6 +60,12 @@
   </si>
   <si>
     <t>Project Peloton</t>
+  </si>
+  <si>
+    <t>Jake Noone</t>
+  </si>
+  <si>
+    <t>In_Active</t>
   </si>
 </sst>
 </file>
@@ -83,12 +89,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -106,7 +118,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -387,15 +399,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -405,19 +418,25 @@
       <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>4</v>
       </c>

--- a/TestData/LV_T2327_TMTC0002473_VerifyTheRolesAvailableToRegistered.xlsx
+++ b/TestData/LV_T2327_TMTC0002473_VerifyTheRolesAvailableToRegistered.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE50F0E8-3110-4CF2-85CB-897B16085081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59E1FAA-1892-4963-B2BC-C636A97A3A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -400,15 +400,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -422,7 +422,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -436,7 +436,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>4</v>
       </c>
@@ -450,17 +450,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0331C7F-1076-4045-A12F-645F65C1D829}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -473,17 +473,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EB80ABF-3E2D-4CF4-8352-E1A55C64BEA2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
